--- a/templates/mallangtalk_script_template.xlsx
+++ b/templates/mallangtalk_script_template.xlsx
@@ -5,10 +5,11 @@
   <sheets>
     <sheet state="visible" name="설명" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="캐릭터" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="호감도단계" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="이벤트" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="대사" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="선택지" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="프로필" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="호감도단계" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="이벤트" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="대사" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="선택지" sheetId="7" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -16,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="172">
   <si>
     <t xml:space="preserve">말랑톡 대본 템플릿</t>
   </si>
@@ -24,12 +25,39 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">[캐릭터] 이름, 상태메시지, 성격·세계관(말투·습관·취미까지 자세히), 타자속도를 적어요.</t>
+    <t xml:space="preserve">[캐릭터] 이름, 상태메시지, 성격·세계관(말투·습관·취미까지 자세히), 타자속도, 한줄소개, 태그(쉼표로)를 적어요.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  이미지주소: 인터넷 이미지 주소 (비워 두고 앱에서 사진을 골라도 돼요)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  대사에 {이름} 이라고 쓰면 플레이어가 정한 별명으로 바뀌어요. 뒤에 붙는 조사(아·이·은·을·과·이랑)도 받침에 맞게 바뀌어요. 예: {이름}아 뭐해? → 쨋뀨야 뭐해?</t>
   </si>
   <si>
     <t xml:space="preserve">  타자속도: 번개같이 / 빠릿빠릿 / 보통 / 느긋하게 / 한참 고민 중 하나, 또는 0.5~2.0 숫자 (클수록 천천히 침)</t>
   </si>
   <si>
+    <t xml:space="preserve">  대표대사: 상세 화면 맨 위에 뜨는 한 줄. 유저설정: 이 이야기에서 플레이어는 누구인지 (예: {이름} · 1년 전 팀플에서 만난 친구)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  비밀: 플레이어에겐 안 보이고 AI 자유대화가 서서히 드러내는 설정. 대표색: #E86A92 같은 색 코드 (비워도 됨)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[프로필] 상세 화면에 보이는 설정 카드예요. 구분에 따라 칸 뜻이 달라요. (시트를 지워도 괜찮아요)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  항목: 제목=나이·직업·생일 같은 이름, 내용=값, 비밀=O 이면 플레이어에겐 숨김</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  성격: 제목=왼쪽 성향(내향), 내용=오른쪽 성향(외향), 수치=오른쪽으로 기운 정도 0~100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  대사: 제목=상황(예: 기분 좋을 때), 내용=대사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  인물: 제목=이름, 내용=관계(예: 룸메이트), 말투=그 사람 말투</t>
+  </si>
+  <si>
     <t xml:space="preserve">[호감도단계] 단계마다 이름과 점수 구간(0~100)을 적어요. 예: 어색한 사이 0~19, 친구 20~49, 썸 50~100</t>
   </si>
   <si>
@@ -111,6 +139,129 @@
     <t xml:space="preserve">타자속도</t>
   </si>
   <si>
+    <t xml:space="preserve">한줄소개</t>
+  </si>
+  <si>
+    <t xml:space="preserve">말수 적은 사진 동아리 선배가 자꾸 출사에 부른다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">태그</t>
+  </si>
+  <si>
+    <t xml:space="preserve">선배, 무뚝뚝, 필름카메라</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이미지주소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대표대사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">찍을 거 없으면 너라도 찍지 뭐.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">유저설정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{이름} · 사진 동아리에 새로 들어온 후배</t>
+  </si>
+  <si>
+    <t xml:space="preserve">비밀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">동아리 첫날 {이름}이 찍은 사진을 보고 관심이 생겼다. 그 사진을 아직 폰에 갖고 있다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대표색</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#5E7C6B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">구분</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제목</t>
+  </si>
+  <si>
+    <t xml:space="preserve">수치·말투</t>
+  </si>
+  <si>
+    <t xml:space="preserve">나이</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25살</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전공</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시각디자인과 4학년</t>
+  </si>
+  <si>
+    <t xml:space="preserve">카메라</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아버지가 쓰던 필름 카메라</t>
+  </si>
+  <si>
+    <t xml:space="preserve">좋아하는 것</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해 질 녘 골목, 블랙커피</t>
+  </si>
+  <si>
+    <t xml:space="preserve">첫인상</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{이름}이 동아리 첫날 찍은 사진을 몰래 저장해 둠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">성격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">내향</t>
+  </si>
+  <si>
+    <t xml:space="preserve">외향</t>
+  </si>
+  <si>
+    <t xml:space="preserve">무뚝뚝</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다정함</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">칭찬받았을 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그건 됐고. 밥은 먹었어.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">걱정될 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어디야. 데리러 갈게.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">인물</t>
+  </si>
+  <si>
+    <t xml:space="preserve">민서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사진 동아리 회장, 이준의 동기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">밝고 말이 많음</t>
+  </si>
+  <si>
     <t xml:space="preserve">단계명</t>
   </si>
   <si>
@@ -153,9 +304,6 @@
     <t xml:space="preserve">시간안내</t>
   </si>
   <si>
-    <t xml:space="preserve">제목</t>
-  </si>
-  <si>
     <t xml:space="preserve">컷씬설명</t>
   </si>
   <si>
@@ -225,13 +373,13 @@
     <t xml:space="preserve">단계</t>
   </si>
   <si>
-    <t xml:space="preserve">대사</t>
-  </si>
-  <si>
     <t xml:space="preserve">빠르기</t>
   </si>
   <si>
     <t xml:space="preserve">사진</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{이름}.</t>
   </si>
   <si>
     <t xml:space="preserve">내일 출사 가는데.</t>
@@ -743,12 +891,57 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -766,50 +959,104 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B6" s="3">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="1"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -820,50 +1067,168 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
+  <cols>
+    <col min="1" max="1" width="8.00" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.00" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="50.00" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.00" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.00" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="4">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4">
-        <v>9</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="4">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4">
-        <v>24</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="4">
-        <v>25</v>
-      </c>
-      <c r="C4" s="4">
-        <v>100</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="4">
+        <v>22</v>
+      </c>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="4">
+        <v>60</v>
+      </c>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -871,6 +1236,59 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="4">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="4">
+        <v>25</v>
+      </c>
+      <c r="C4" s="4">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <cols>
@@ -888,63 +1306,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="C2" s="4">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="K2" s="4">
         <v>2</v>
@@ -952,85 +1370,85 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="C3" s="4">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="C4" s="4">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="C5" s="4">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="C6" s="4">
         <v>99</v>
@@ -1042,10 +1460,10 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -1055,7 +1473,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <cols>
@@ -1069,286 +1487,300 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>68</v>
+        <v>117</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="B2" s="4">
         <v>1</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" s="3">
-        <v>1.2</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="B3" s="4">
         <v>1</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="E3" s="3">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="F3" s="1"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="B4" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="E4" s="3">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="F4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="B5" s="4">
         <v>2</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="1"/>
+        <v>123</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.8</v>
+      </c>
       <c r="F5" s="1"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="B6" s="4">
         <v>2</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0.9</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="E6" s="1"/>
       <c r="F6" s="1"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="4">
+        <v>97</v>
+      </c>
+      <c r="B7" s="4">
         <v>2</v>
       </c>
+      <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="E7" s="3">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="F7" s="1"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="C8" s="4">
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="E8" s="3">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="F8" s="1"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="4">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1"/>
+        <v>97</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2</v>
+      </c>
       <c r="D9" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" s="1"/>
+        <v>128</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1.2</v>
+      </c>
       <c r="F9" s="1"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="B10" s="4">
         <v>1</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="E10" s="1"/>
-      <c r="F10" s="1" t="s">
-        <v>81</v>
-      </c>
+      <c r="F10" s="1"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="B11" s="4">
         <v>1</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" s="3">
-        <v>0.9</v>
-      </c>
-      <c r="F11" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="B12" s="4">
         <v>1</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="E12" s="3">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="F12" s="1"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="B13" s="4">
         <v>1</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="E13" s="3">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="F13" s="1"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="B14" s="4">
         <v>1</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1" t="s">
-        <v>86</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="F14" s="1"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="B15" s="4">
         <v>1</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1.3</v>
-      </c>
-      <c r="F15" s="1"/>
+        <v>134</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="B16" s="4">
         <v>1</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="E16" s="3">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="F16" s="1"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="B17" s="4">
         <v>1</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="E17" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" s="4">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18" s="3">
         <v>1.4</v>
       </c>
-      <c r="F17" s="1"/>
+      <c r="F18" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <cols>
@@ -1364,45 +1796,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>94</v>
+        <v>143</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>95</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="B2" s="4">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>98</v>
+        <v>147</v>
       </c>
       <c r="F2" s="4">
         <v>7</v>
@@ -1414,43 +1846,43 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="B3" s="4">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>100</v>
+        <v>149</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>101</v>
+        <v>150</v>
       </c>
       <c r="F3" s="4">
         <v>0</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="B4" s="4">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>102</v>
+        <v>151</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="F4" s="4">
         <v>3</v>
@@ -1460,19 +1892,19 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="B5" s="4">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>106</v>
+        <v>155</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>107</v>
+        <v>156</v>
       </c>
       <c r="F5" s="4">
         <v>0</v>
@@ -1482,19 +1914,19 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="B6" s="4">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>108</v>
+        <v>157</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>109</v>
+        <v>158</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="F6" s="4">
         <v>6</v>
@@ -1504,19 +1936,19 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="B7" s="4">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>111</v>
+        <v>160</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>113</v>
+        <v>162</v>
       </c>
       <c r="F7" s="4">
         <v>2</v>
@@ -1526,19 +1958,19 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="B8" s="4">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>114</v>
+        <v>163</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>115</v>
+        <v>164</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
       <c r="F8" s="4">
         <v>3</v>
@@ -1548,19 +1980,19 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="B9" s="4">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="F9" s="4">
         <v>0</v>
@@ -1570,19 +2002,19 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="B10" s="4">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>122</v>
+        <v>171</v>
       </c>
       <c r="F10" s="4">
         <v>5</v>
